--- a/TF_PreSeed_Investor_List_30Sep2026.xlsx
+++ b/TF_PreSeed_Investor_List_30Sep2026.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angels (people)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angel networks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Micro-VCs &amp; angel funds" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grants &amp; non-VC money" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Angels (people)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Angel networks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Micro-VCs &amp; angel funds" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Accelerators" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Grants &amp; non-VC money" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Angels (people)'!$A$1:$O$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Angel networks'!$A$1:$O$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Micro-VCs &amp; angel funds'!$A$1:$O$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Grants &amp; non-VC money'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Accelerators'!$A$1:$S$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Grants &amp; non-VC money'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +65,15 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +105,11 @@
         <fgColor rgb="00DDE4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -114,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -144,6 +158,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -511,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -532,7 +555,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -570,159 +593,246 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Accelerators: 98 programs checked on 30 Sep 2026. Cash-for-equity accelerators, corporate and sector programs (Meta, Razorpay, cloud credits, food tech), and government, university and East India programs. 31 are tagged Skip (closed, wrong country or wrong fit) so you can see they were checked. Some also appear on other tabs; the 'Also on tab' column says where.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>A: pitch first. They've backed restaurant tech, WhatsApp tools, SMB merchant software, or have an Odisha / East India link.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>B: good fit. Food or SMB operators and active pre-seed angels.</t>
+          <t>A: pitch first. They've backed restaurant tech, WhatsApp tools, SMB merchant software, or have an Odisha / East India link.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>C: long shot or conditional (Zomato/Swiggy conflict, weak sector fit, only if a founder qualifies).</t>
+          <t>B: good fit. Food or SMB operators and active pre-seed angels.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>C: long shot or conditional (Zomato/Swiggy conflict, weak sector fit, only if a founder qualifies).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Later: right investor, wrong round. Keep warm for the next raise.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Skip (Accelerators tab only): checked on 30 Sep 2026 and closed, wrong country or wrong fit. Kept so you don't re-check them. The Accelerators tab says 'A: apply first' instead of 'A: pitch first'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>A realistic way to stack the Rs 1.7 to 2.5 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1. Local anchor, Rs 25 to 75L: Odisha and Kolkata F&amp;B and business-family angels via TiE Bhubaneswar, Startup Odisha, Abhishek Rungta, Sagar Daryani, Apurva Salarpuria, Foxhog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2. One first-cheque fund, Rs 75L to 1.25 Cr: First Cheque (Rs 75L standard) or 100X.VC (Rs 1.25 Cr fixed). Axilor, Whiteboard or Artha if you want someone who already knows restaurant or WhatsApp SaaS.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3. Operator angels, Rs 10 to 50L each: the tier A people who backed Petpooja, UrbanPiper, DotPe, Reelo, Thrive, Gallabox, BiteSpeed.</t>
+          <t>1. Local anchor, Rs 25 to 75L: Odisha and Kolkata F&amp;B and business-family angels via TiE Bhubaneswar, Startup Odisha, Abhishek Rungta, Sagar Daryani, Apurva Salarpuria, Foxhog.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>4. Fill the gap through one syndicate (IPV, LVX or Hyderabad Angels) so the cap table stays clean.</t>
+          <t>2. One first-cheque fund, Rs 75L to 1.25 Cr: First Cheque (Rs 75L standard) or 100X.VC (Rs 1.25 Cr fixed, but its program looks paused, so confirm first). Axilor, Whiteboard or Artha if you want someone who already knows restaurant or WhatsApp SaaS.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>3. Operator angels, Rs 10 to 50L each: the tier A people who backed Petpooja, UrbanPiper, DotPe, Reelo, Thrive, Gallabox, BiteSpeed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>4. Fill the gap through one syndicate (IPV, LVX or Hyderabad Angels) so the cap table stays clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>5. Stack free money on top: GENESIS 1:1 match (up to Rs 50L), Startup Odisha grants (Rs 2.4L allowance + up to Rs 15L once Rs 25L equity lands), SIDBI challenge (deadline 16 Oct 2026).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Things to know before sending anything</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Most state and central money needs the new Table Foundry Pvt Ltd, registered in Bhubaneswar, with DPIIT recognition. MSM Global (Gorakhpur) doesn't qualify for Odisha money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SIDBI Innovation Challenge closes 16 Oct 2026. It fits if TF is pitched as AI-led market access for small restaurants (MSMEs). This is the one hard deadline right now.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Startup India Seed Fund closed to new applicants on 31 May 2026. Don't count on it.</t>
+          <t>Most state and central money needs the new Table Foundry Pvt Ltd, registered in Bhubaneswar, with DPIIT recognition. MSM Global (Gorakhpur) doesn't qualify for Odisha money.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Kunal Shah became head of WhatsApp at Meta in June 2026. Big signal for a WhatsApp product, but he may have paused personal cheques.</t>
+          <t>SIDBI Innovation Challenge closes 16 Oct 2026. It fits if TF is pitched as AI-led market access for small restaurants (MSMEs). With Kotak BizLabs (6 Oct) and YC (2 Nov), it is one of three hard deadlines right now.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Zomato and Swiggy founders and execs still at those companies are tagged as a conflict. Ex-Zomato people (Pankaj Chaddah, Mohit Gupta, Gaurav Gupta) are fine.</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Kotak BizLabs Season 3 (grant up to Rs 30L, no equity) closes 6 Oct 2026 and needs DPIIT recognition by then. Only realistic if DPIIT lands this week, or if MSM Global already has it. Pick IIMCIP Kolkata as the partner and frame TF as fintech or inclusive tech.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AngelBay's rules exclude non-veg restaurants. Ask before pitching.</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>YC Winter 2027 closes 2 Nov 2026. YC only invests in US, Canada, Singapore or Cayman companies, so applying means a parent company abroad with the Indian Pvt Ltd under it. Decide this before registering Table Foundry Pvt Ltd.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Cheerio AI (WhatsApp engagement SaaS) raised Rs 8 Cr seed in Mar 2026 from Artha, Hyderabad Angels, TiE Angels and LVX. Use it as the comparable deal in the pitch.</t>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Meta launched Business AI on WhatsApp for Indian small businesses (May 2026) and Meta Business Agent in India (July 2026). Investors will ask how TF is different. No WhatsApp or Meta startup accelerator is open to Indian companies right now (the WhatsApp AI Startups Hub is Brazil only).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn links are only given where one was seen in a source. Otherwise the cell says 'search: name linkedin'. Cheque sizes marked 'est.' are estimates.</t>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>100X.VC's apply page returns an error and its last public cohort was Jan 2025. Email them before counting on the Rs 1.25 Cr cheque.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Startup India Seed Fund closed to new applicants on 31 May 2026. Don't count on it.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Kunal Shah became head of WhatsApp at Meta in June 2026. Big signal for a WhatsApp product, but he may have paused personal cheques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Zomato and Swiggy founders and execs still at those companies are tagged as a conflict. Ex-Zomato people (Pankaj Chaddah, Mohit Gupta, Gaurav Gupta) are fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AngelBay's rules exclude non-veg restaurants. Ask before pitching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Cheerio AI (WhatsApp engagement SaaS) raised Rs 8 Cr seed in Mar 2026 from Artha, Hyderabad Angels, TiE Angels and LVX. Use it as the comparable deal in the pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn links are only given where one was seen in a source. Otherwise the cell says 'search: name linkedin'. Cheque sizes marked 'est.' are estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Accelerators: where TF fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Incubation: TF doesn't need it for desks or mentoring. But KIIT-TBI and FTBI NIT Rourkela are the doors to SAMRIDH, GENESIS and NIDHI money, so join one as an incubatee once the Odisha Pvt Ltd exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Cash accelerators: TF is on time. YC, Peak XV Surge and Accel Atoms take companies with a few paying customers. Talent programs (Entrepreneur First, South Park Commons, Antler's residency) want people before a company, so TF is past them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Too early for: Google for Startups Accelerator India (wants seed), Upekkha (now about $100K ARR and no cash), T-Hub T-Angel (Rs 3 to 5L monthly revenue), Mastercard Start Path (seed raised). Tagged Later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Cheque size: YC, Surge and Atoms write $500K to $2M, more than the planned round. A yes from any of them changes the size and shape of the raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Order of work: 1) incorporate Table Foundry Pvt Ltd, 2) DPIIT and Startup Odisha recognition, 3) Meta WhatsApp Tech Provider enrollment plus Razorpay Rize and Partner Program, 4) KIIT-TBI incubation, 5) Surge and Atoms (rolling), and YC by 2 Nov only if you're willing to set up a parent abroad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Use the Status column (dropdown) on each tab to track outreach.</t>
         </is>
@@ -10421,7 +10531,11 @@
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep check: apply page returns an error, last public cohort Jan 2025. Email before counting on it. See Accelerators tab.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -11493,7 +11607,11 @@
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep check: no cash now (2 to 4% equity for services), wants about $100K ARR. Moved to Later on Accelerators tab.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -12565,7 +12683,11 @@
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep check: Surge 12 announced 28 Sep, applications rolling, led BiteSpeed's seed. Tier A on Accelerators tab.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -13243,6 +13365,8378 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Run by / base</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>What you get</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Equity taken?</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Stage they take</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant alumni</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Next deadline / cohort</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Apply URL</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Fit for TF</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Also on tab</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Next step / notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Y Combinator (W27 batch)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Y Combinator / San Francisco</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>$500K: $125K SAFE for 7% plus $375K uncapped MFN SAFE; $12M+ partner credits</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 7% plus MFN SAFE conversion (about 2.5% at a $15M cap)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Idea to early revenue</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay, Meesho, Zepto, Bikayi (WhatsApp store builder for SMBs)</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>2 Nov 2026, 8pm PT; decisions by 11 Dec 2026; batch Jan to Mar 2027 in SF</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/apply</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Worth a shot: SMB vertical AI with paying users is in scope, but acceptance is around 1% and TF would need a US/Singapore parent (flip) before YC invests.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/apply ; https://www.ycombinator.com/deal</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Surge by Peak XV</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Seed program (rolling)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Peak XV Partners / Bengaluru, Singapore</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>$500K to $5M seed equity (ceiling raised from $3M in Sep 2026); 8-week Immersion each September; ongoing platform</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Yes, negotiated</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Idea to seed; FAQ says no minimum traction</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>BiteSpeed (WhatsApp/chat commerce, Surge-led seed and pre-Series A)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Rolling, year round; Surge 12 announced 28 Sep 2026; next Immersion Sep 2027</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://surge.peakxv.com</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Strong fit: invests in Indian entities, backed a WhatsApp commerce SaaS, and 3 paying restaurants is enough to start a conversation; cheque could exceed TF's planned round.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>https://surge.peakxv.com/faqs ; https://techcrunch.com/2026/09/28/peak-xv-goes-bigger-at-seed-with-new-surge-cohort-as-series-a-bar-rises/</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Accel Atoms (AI Cohort and Atoms X)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed program</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Accel India (AI cohort co-invested with Google AI Futures Fund; Atoms X with Prosus) / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>AI cohort: up to $2M equity or convertible note plus up to $350K compute credits; Atoms X: up to $1M equity</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Yes, negotiated</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed; raised under $2M; pre-product or pre-revenue preferred</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Not verified for restaurant or chat commerce</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Rolling; last AI cohort deadline was 26 Jan 2026, next cohort timing TBA</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://atoms.accel.com</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Good fit if TF pitches as AI-first; must be incorporated before final selection, which the new Pvt Ltd solves.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Micro-VCs &amp; angel funds</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>https://atoms.accel.com/faqs</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Meta WhatsApp Tech Provider enrollment</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Platform partner program (not an accelerator)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Meta / WhatsApp Business Platform; global, online</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Official API access to onboard and message on behalf of many restaurant WhatsApp numbers via Embedded Signup; access to Meta support channels. No cash or credits.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Any incorporated business that passes Meta Business Verification and App Review</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>All WhatsApp ISVs (Meta required ISVs to enroll as Tech Providers by 30 Jun 2025)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Rolling. Needs verified Meta business portfolio (so do it once Table Foundry Pvt Ltd exists)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>https://developers.facebook.com/documentation/business-messaging/whatsapp/solution-providers/get-started-for-tech-providers</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Core infrastructure for TF, and the prerequisite for any later Meta partner status; not optional.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>https://developers.facebook.com/documentation/business-messaging/whatsapp/solution-providers/get-started-for-tech-providers</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay Rize</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Corporate founder community and perks program</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay; Bengaluru, online</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Founder community (Rize Tech+), pitch deck help (Pitch Perfect), YC application prep, about $11K credits across GCP, AWS, Azure, OpenAI, company registration help, access to Razorpay team</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to early stage, bootstrapped welcome</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>1,750+ founders in community; Razorpay also runs a MeitY Startup Hub tie-up giving AI startups free Razorpay products and Rize cohorts</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>https://rize-dashboard.razorpay.com/register</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Free, fast, and TF already runs on Razorpay Route, so it is the easiest way into Razorpay's team and investor network.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/rize/</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay Partner Program (Technology Partner, SaaS/ISV track)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Distribution / revenue-share partner program</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay; online</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Recurring commission on payments your merchants process through Razorpay, partner dashboard, APIs and docs, co-listing as a SaaS/ISV partner</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Any platform that onboards merchants onto Razorpay</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>SaaS platforms, BSPs and ISVs (Razorpay names storefronts, CPaaS and BSPs)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Rolling, online onboarding</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/partners/</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>TF onboards restaurants onto Razorpay Route, so this adds a second revenue line and a partner relationship at no cost.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/partners/</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Kotak BizLabs Season 3</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Corporate CSR accelerator with grant</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank CSR, via T-Hub, IIM Calcutta Innovation Park, IIMA Ventures, NSRCEL (IIMB), FITT (IIT Delhi)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Grant up to Rs 30 lakh, 6 to 8 month program, bootcamp (IIMA, Nov 2026), mentors, investor demo days</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT-recognised, revenue-generating, market-ready product with paying customers</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Season 2 picked 71 startups (Apr 2026); sector mix is agri, climate, fintech, health</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>6 Oct 2026 (T-Hub page; IIMA page says 9 Oct). Not extendable</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>https://kotakbizlabs.accubate.app/ext/form/24005/1/apply</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Best near-term non-dilutive money; pitch as FinTech/Inclusive Tech for small restaurants. Needs DPIIT recognition by the deadline, so push Table Foundry incorporation and DPIIT now, or apply via MSM Global only if it is already DPIIT-recognised. Choose IIMCIP Kolkata as partner.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.t-hub.co/kotak-bizlabs-s3</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT Startup India recognition + MeitY Startup Hub (MSH) profile</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Gateway (required for govt money)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT, Govt of India / MeitY Startup Hub, New Delhi</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Recognition certificate; unlocks SAMRIDH, GENESIS, NIDHI-SSS, Kotak BizLabs, tax benefits. MSH portal is where SAMRIDH and GENESIS applications are filed</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Pvt Ltd under 10 years, turnover under Rs 100 Cr</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Rolling; usually a few working days after incorporation</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Do this the week Table Foundry Pvt Ltd gets its CIN. Almost every row below needs it.</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.youthnet.org.in/inviting-application-for-the-meity-genesis-investment-2-0-program/</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>KIIT-TBI incubation (gateway to NIDHI-SSS, SAMRIDH, GENESIS)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Incubator (scheme gateway)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>KIIT Technology Business Incubator, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Incubation, mentors, Startup Odisha recognised incubator; hosts NIDHI-SSS (up to Rs 1 Cr soft loan or equity), NIDHI Accelerator, SAMRIDH, GENESIS, TIDE 2.0, own seed fund (equity up to Rs 30L)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Incubation: check policy. Seed/NIDHI: equity or debt</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Any stage; form asks monthly revenue, so revenue-stage is fine</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Bariflo Labs, LarkAI, Avay Bioscience, Minion Labs, Mokkomoto</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Incubation form rolling. Seed fund and NIDHI Accelerator currently closed; NIDHI-SSS calls open for about 1 month at a time. KIIT LaunchPad 2026 (AI track, up to Rs 1 Cr) closed 15 May 2026</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>https://kiitincubator.in/incubate/</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Join as an incubatee now so TF is first in line when NIDHI-SSS, SAMRIDH or GENESIS windows open. Many of these need a few months of association, and the new Odisha Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>https://kiitincubator.in/</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>A: apply first</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha recognition and incentives</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>State scheme (gateway to Odisha money)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha, MSME Dept, Govt of Odisha</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Sustenance allowance Rs 20,000/month for 1 year; product development and marketing assistance up to Rs 15L; Odisha Startup Growth Fund (Rs 100 Cr FoF via SIDBI)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Registered in Odisha (or 50% workforce in Odisha), under 5 years old (policy 2016 text), plus traction tests: e.g. Rs 50K to 10L monthly revenue for allowance; Rs 25L equity raised or Rs 10L monthly revenue for 6 months for the Rs 15L grant</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>195 startups got financial assistance</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Rolling on the Startup Odisha portal</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>https://startupodisha.gov.in/</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Main Odisha money route. MSM Global (UP) cannot claim it; Table Foundry Pvt Ltd can, after recognition. Amounts are from the 2016 policy page; check for the current policy.</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/state-startup-policies/Odisha-state-policy.html</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Antler India</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed residency / fund</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Antler / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>About Rs 4 Cr (~$425K) for 11%; Rs 2L relocation grant; up to $4M perks</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 11%</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pre-launch, pre-product or pre-revenue teams; day zero</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Between cohorts; next residency TBA; site says reach out directly</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.antler.co/residency/india</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>TF is past Antler's residency stage, but Antler India also meets companies directly; worth a direct email rather than waiting for a cohort.</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Micro-VCs &amp; angel funds</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.antler.co/residency/india</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>100Unicorns</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Accelerator fund</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>100Unicorns (formerly 9Unicorns) / Mumbai</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>$250K to $300K initial, follow-on up to $3M</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Idea to product</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Shiprocket, Zingbus</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Cohort-based, dates not published</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.100unicorns.vc</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Cheque size fits TF's round; very active (48 deals in 2025).</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.peony.ink/blog/accelerators-india ; https://tracxn.com/d/accelerator-incubator/100unicorns/__tQ24X66vlq6ocJvNWwd9VdscFNWNIts4_vFGI0M1xII</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA Inception</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Credits and perks program</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA; global, India page</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Partner cloud credits (e.g. AWS Activate up to $100K, Nebius), DLI training, hardware/software discounts, VC intros via Inception Capital Connect, co-marketing badge</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Incorporated, at least 1 developer, working website, under 10 years old</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Thousands of AI startups worldwide including many Indian ones</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Rolling, no cohorts</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>https://programs.nvidia.com/phoenix/application</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Easy yes once the Pvt Ltd is incorporated; main value is unlocking bigger partner cloud credits for TF's AI layer.</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-in/startups/</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft for Startups (formerly Founders Hub)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft; global, online</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Azure credits from $1K (90 days) then $4K once verified, growing to up to $150K with usage; more if referred by an Investor Network partner; Azure OpenAI access</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Software startups up to pre-Series C; not agencies or consultancies</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Broad; program revamped in May 2026 with activation via Azure portal</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Rolling, decisions in about 3 business days</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>https://startups.microsoft.com</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Useful for Azure OpenAI or model hosting credits; ask any pre-seed investor for an Investor Network referral code to start higher.</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/startups/microsoft-for-startups/overview</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Google for Startups Cloud Program</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Google Cloud; global, online</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Start tier about $2K credits for pre-funded startups; Scale and AI tiers up to $200K, or $350K for AI-first, usually needing institutional funding</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Start tier: pre-funded, under 5 years; higher tiers need a funded round</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/startup</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Take the Start tier now for Gemini/Firebase; reapply for the AI tier right after the pre-seed closes.</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/startup/benefits</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>AWS Activate (DPIIT offer and Founders package)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>AWS with Startup India / Invest India</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>$5,000 AWS credits for DPIIT-recognised startups plus partner offers; or $1,000 Founders package for self-funded startups</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Self-funded to pre-Series B, under 10 years, working website</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Rolling (DPIIT offer needs DPIIT ID)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/activate</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Free hosting runway; claim the $5K DPIIT offer as soon as recognition comes through.</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/reources/resource-partners/cloud-services/aws_services.html</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Zoho for Startups</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Zoho via Startup India; Chennai, online</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 1.86 lakh Zoho Wallet credits for DPIIT startups (up to Rs 3 lakh for tax-exempt or SISFS startups), valid 360 days</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT-recognised, no prior paid Zoho subscription</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Rolling after DPIIT</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/reources/resource-partners/application-based-services/zoho.html</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Covers TF's own CRM, books and helpdesk for a year at no cost; low effort once DPIIT is in.</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/reources/resource-partners/application-based-services/zoho.html</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MeitY SAMRIDH via KIIT-TBI (Cohort 2 accelerator)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Govt accelerator (matched investment)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>KIIT Technology Business Incubator, Bhubaneswar (MeitY Startup Hub scheme)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>MSH invests avg Rs 30L, up to Rs 40L, matching an equal private investment; 6-month acceleration, masterclasses, demo day</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Yes. MSH money goes in as SAFE converting to CCPS; accelerator may also take a stake</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT Pvt Ltd, 51% Indian, product with traction, needs private investor commitment (IIM Udaipur SAMRIDH asks Rs 40L hard commitment)</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>KIIT SAMRIDH cohorts: LarkAI Healthcare, Avay Bioscience, LVL Alpha; several raised Rs 50L to 2.85 Cr</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>KIIT page says call closed. KIIT holds 6 Cohort-2 slots (MSH order 3 Mar 2025). Next call TBA; ask tbi@kiitincubator.in if slots remain</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>https://kiitincubator.in/samridh-accelerator/</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>The closest SAMRIDH accelerator to TF, in Bhubaneswar. Your pre-seed angels could be the matching money. Needs Odisha Pvt Ltd plus DPIIT first. Taking SAMRIDH bars you from GENESIS.</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>https://msh.meity.gov.in/assets/samridh2ndcohrot/SAMRIDH%202nd%20Cohort%20OM%20Final.pdf</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>MeitY GENESIS Matching Investment (Investment 2.0) via KIIT-TBI GENESIS Centre</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Govt scheme (matched equity) via incubator</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>MeitY Startup Hub; KIIT-TBI Bhubaneswar is a GENESIS centre (also FTBI Rourkela, IIT Patna IC)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 50L (avg Rs 40L) equity, matched 1:1 to private investment raised; mentoring, investor pitching</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Yes, GENESIS takes an equity stake</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT Pvt Ltd registered in a Tier-II/III city (Bhubaneswar qualifies), market-ready, revenue preferred, qualifying VC/angel money</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Investment 2.0 closed 24 Sep 2026. Previous round closed 31 Oct 2025, so next call likely around H2 2027. Not eligible if you took SAMRIDH or TIDE scale-up</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>https://mshportal.meity.gov.in/ext/form/24189/1/apply</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Strong fit once the pre-seed closes: the angel cheque can be matched for up to Rs 50L. Register the Pvt Ltd in Bhubaneswar (not a metro) and get DPIIT first. Choose SAMRIDH or GENESIS, not both.</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>https://kiitincubator.in/genesis-centre/</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>AIC-Nalanda SURGE (annual incubation cohort)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Atal Incubation Centre (AIM)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>AIC-Nalanda Institute of Technology Foundation, Bhubaneswar (Odisha's first AIC)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>12-month cohort, seed fund up to Rs 25L, mentoring, branding, investor connects</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Likely for seed fund; confirm</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>PoC or functional prototype; sectors incl Financial Inclusion, IoT, Education</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>150+ startups incubated</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>SURGE 5.0 ran 2025; next SURGE cohort TBA</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aicnalanda.com/page/surge-4</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Local AIC with seed money; a realistic cohort for a Bhubaneswar SaaS once the Odisha Pvt Ltd exists.</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aicnalanda.com/page/surge-4</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Odisha Tourism Acceleration Program (OTAP)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Regional accelerator (sector)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>AIC-Nalanda with Merstra Foundation, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>16-week hybrid accelerator: masterclasses, mentors, pilot opportunities in Odisha tourism, investor access, credits; free</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>No fee; equity not stated</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage with initial traction in tourism, travel, hospitality</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Launched Jan 2025 (National Startup Day). 2026 edition not announced; deadline to be posted on OTAP site</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>https://forms.gle/UMvLp68YMep69SLS8</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Only Odisha accelerator that explicitly covers hospitality. Restaurants in Puri/Bhubaneswar tourist belts give TF a clear pitch.</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>https://otap.aicnitf.in/</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>O-Hub (Odisha Startup Hub)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>State govt incubator</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha, MSME Dept, Govt of Odisha, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Incubation space (4 lakh sq ft, 400 seats), mentors, investor connect, business development; 26 startups picked in Jan 2025 intake</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Odisha startups</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Current intake shows application closed; next intake TBA</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>https://ohub.odisha.gov.in/</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Good base and signal to Startup Odisha once TF is an Odisha Pvt Ltd; not a cash program itself.</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/startup_odisha/status/1881687593060114727</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>TiE Bhubaneswar programs</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Regional network / mentoring</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>TiE Bhubaneswar chapter</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Startup Open MiC Connect (mentoring, investor engagement), TiEcon Bhubaneswar, access to TiE angels</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Open MiC held 31 Jan 2026; TiEcon Bhubaneswar last held 2025; 2026 dates not published</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>https://bhubaneswar.tie.org/special-events/</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>No cash, but the best local room for Odisha angels for the pre-seed round.</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Angel networks</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>https://events.tie.org/TiEBhubaneswarStartupOpenMiCConnectProgramme</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IIM Calcutta Innovation Park (IIMCIP) incubation and seed</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>University incubator (scheme gateway)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>IIM Calcutta Innovation Park, Kolkata</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Physical or virtual incubation; seed funds as equity or debt under NIDHI-SSP, NIDHI Seed Support, CSR; Rs 26 Cr seed given, Rs 1,946 Cr follow-on raised by incubatees; also a Kotak BizLabs S3 partner</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Yes for seed (equity/debt)</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Early to growth; NIDHI-SSP needs DPIIT and 3 months of association</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>103-startup portfolio; SAMRIDH cohort 1 host</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Incubation rolling. Other live calls (IDFC IGNITE, Prakriti NE, Maruti Nurture) are sustainability or North East focused</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>http://iimcip.org/incubation/seed-funding/</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Strongest East India brand that also writes seed cheques; virtual incubation works from Bhubaneswar. Apply for Kotak BizLabs through IIMCIP.</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Angel networks</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>https://iimcip.org/news-event/announcements/</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>B: good fit</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Nasscom GenAI Startup Foundry</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Industry body accelerator</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Nasscom AI, pan-India (virtual)</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Cloud credits, global mentors, 60+ partners, soft investor commitments worth $25M</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>GenAI-centred product, MVP, at least 1 paying client or 3 paid PoCs</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>33 startups in cohort 4 (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Cohort 5 applications open; deadline not published</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>https://nasscom.in/ai/genaifoundry/</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>TF qualifies on traction if the pitch leads with its AI agent for WhatsApp ordering and campaigns. Can apply with MSM Global or the new entity.</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ciol.com/news/nasscom-genai-foundry-fourth-cohort-india-ai-startups-2026-11749733</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>100X.VC</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed fund (cohort classes)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>100X.VC / Mumbai</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Historically Rs 1.25 Cr via iSAFE for up to 15%, plus HomeRun masterclass and VC pitch day</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Yes, up to 15% via iSAFE</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed, first cheque</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>180+ startups incl. B2B SaaS; not verified for restaurant tech</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Unclear: last public cohort was Class 12 (Jan 2025); apply page now returns 404</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.100x.vc</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Cheque size matches TF's round well, but the program looks paused or restructured; email the team to confirm before spending time.</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Micro-VCs &amp; angel funds</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.100x.vc (site pared back; /apply 404, checked 30 Sep 2026) ; https://yourstory.com/2025/01/100xvc-invests-27m-18-startups-12th-cohort</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Entrepreneur First Bangalore (Winter 27)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Talent investor / cofounder program</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Entrepreneur First / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>$125K post-money SAFE for 8% plus $125K uncapped MFN SAFE (only if you move to SF and form a Delaware C-corp); Rs 3.6L equity-free stipend</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 8% plus MFN</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Individuals before a team or company</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Early deadline 5 Oct 2026; cohort starts Jan/Feb 2027, full time in person</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>https://apply.joinef.com/app/bangalore-winter/</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Wrong shape: EF is built for individuals finding cofounders, not a company with paying customers.</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.joinef.com/faqs/bangalore/ ; https://apply.joinef.com/app/bangalore-winter/</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>a16z speedrun (SR008)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Andreessen Horowitz / San Francisco</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Up to $1M: $500K SAFE for 10% upfront plus $500K in next round within 18 months; $10M+ credits</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 10%</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Early stage; prefers first institutional cheque</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Not verified for SMB SaaS</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Priority window 12 Oct to 1 Nov 2026; rolling after; program late Jan to Apr 2027 in SF (in person)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>https://speedrun.a16z.com/apply</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Accepts Indian founders, but focus leans to games, consumer and AI apps and it needs 12 weeks in SF.</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>https://speedrun.a16z.com/faq ; https://speedrun.a16z.com/apply</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>500 Global 500 Fellowship (Batch 37)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator (with fee)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>500 Global / San Francisco</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Up to $50K on acceptance, possible $1M later; Phase 1 program fee $35K per startup</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Yes, terms not published on page</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Day zero to first users or revenue</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>6,000+ founders globally; not verified for restaurant tech</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Deadline 2 Oct 2026; program 30 Nov 2026 to 9 Apr 2027 in SF</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>https://500.co/founders/flagship</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Poor value for TF: net cash is small after the $35K fee and it needs months in SF.</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>https://500.co/founders/flagship</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>PearX (W27)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Pear VC / San Francisco</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>$500K to $2M depending on stage; $1M+ credits</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Yes, negotiated</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed; most have not raised before</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>W27 applications open; regular deadline reported as 4 Oct 2026; program Jan to Apr 2027 (must relocate to SF Bay Area)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>https://pear.vc/pearx/</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>US-market focused and needs relocation; low odds for an India-only restaurant SaaS.</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>https://pear.vc/pearx/ ; https://startupintros.com/resources/pearx-w26</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>South Park Commons Founder Fellowship</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Founder fellowship</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>South Park Commons / SF, NYC, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>$400K for 7% on a SAFE plus $600K guaranteed in next round; up to $1M credits</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 7%</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>-1 to 0 (pre-idea to early)</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026 closed (deadline was 2 Aug 2026); Spring 2027 applications to open later in 2026</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.southparkcommons.com/apply/</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Bengaluru option helps, but SPC wants frontier builders exploring ideas, not a restaurant SaaS with customers.</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.southparkcommons.com/news/f26-founder-fellowship/ ; https://www.southparkcommons.com/india/</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Arka Venture Labs</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Cross-border B2B accelerator fund</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Arka (with BGV, Blume) / Bengaluru, Silicon Valley</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Up to $200K to $500K via equity, SAFE or note</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed B2B going global</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>B2B SaaS going to the US</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arka.vc</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Weak fit: built for Indian B2B selling into the US; TF is India-market SMB.</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>https://hub.waveup.com/funds/arka-ventures</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Kalaari CXXO</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed / seed fund for women CEOs</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Kalaari Capital / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>$500K to $1.5M cheques from a $10M fund</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed, ideally MVP with early traction</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>10 portfolio companies</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Rolling; term sheet in 4 to 6 weeks</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>https://cxxo.kalaari.com</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Only if TF's CEO is a woman; otherwise skip.</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>https://cxxo.kalaari.com</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Founder Institute Bengaluru (Spring 2027)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed training program (no cash)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Founder Institute / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>No cash; $499 to $999 fee; mentors, 10 sessions plus Demo Day</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 2.5% warrant (activates on $100K+ raise)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Idea to early</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Global network of 40,000+ mentors</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Early deadline 17 Nov 2026; final 9 Feb 2027; starts 23 Feb 2027</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>https://fi.co/program/bangalore</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Low value for TF: no cash and TF is already past the idea stage.</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>https://fi.co/program/bangalore</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>SaaSBoomi SGx (now AIBoomi)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>SaaS accelerator (no cash)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>SaaSBoomi / AIBoomi community, India</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Free, no equity; 16 weeks of 1:1 SaaS mentors</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Early SaaS (selection by member invite)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Indian SaaS founders</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Registrations closed; next cohort TBA; needs member invitation</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>https://saasboomi.org/initiatives/sgx/</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Good SaaS mentoring, but invite-only and no cash.</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>https://saasboomi.org/initiatives/sgx/</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp AI Startups Hub</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator / partner hub</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Meta / WhatsApp; Sao Paulo, Brazil only</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Meta access and support for startups building AI agents on WhatsApp (payments, ads, Llama); exact perks not published</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>No (as reported)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Tested product, active customers, proven results</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Passabot, Segura, EasyFin, Wellon Digital (about 100 of 200+ applicants)</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Brazil only, launched 23 Sep 2025; no India edition announced</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>The only WhatsApp-specific startup program found; not open to India, but worth asking Meta India contacts whether an India hub is planned.</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.easyfin.blog/en/post/whatsapp-ai-startup-hub-brasil</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>HDFC Bank Parivartan Startup Grants (FY26)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Corporate CSR grant via incubators</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>HDFC Bank CSR through partner incubators (KIIT-TBI Bhubaneswar has been a partner)</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Non-dilutive grant for pilots and validation; Rs 20 Cr pool across incubators</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage social-impact startups picked by partner incubators</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>500+ startups since 2017, about 40% from Tier II/III cities</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Set by each partner incubator; FY26 edition announced 20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Via partner incubator (ask KIIT-TBI)</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Only works with a 'livelihoods for small restaurants / MSME innovation' framing and an incubator sponsor; ask KIIT-TBI if they hold an FY26 allocation.</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>https://thecsruniverse.com/articles/hdfc-bank-to-disburse-20-crore-to-social-impact-start-ups-under-fy26-parivartan-grants</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Flipkart Leap Ahead</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Corporate VC accelerator</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Flipkart Ventures; Bengaluru</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>$200K to $500K investment, 60-day program, Flipkart mentors, demo day</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Yes (equity investment, % not published)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to Series A, MVP, full-time founders</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>20+ startups since 2022</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Last call was Leap Ahead 4.0 (Jul 2025); no 2026 cohort or investment seen</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkartleap.com/leap-ahead/</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Themes are AI-native, drones and quick-commerce enablement; TF is a stretch and the program looks quiet in 2026.</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>https://indianstartupnews.com/news/flipkart-ventures-launches-leap-ahead-40-to-support-early-stage-startups-9482605</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n"/>
+      <c r="S39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Amazon Smbhav Venture Fund</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Corporate VC (not an accelerator)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Amazon India; Bengaluru</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Equity investment; fund now $350M; focus includes digitising small businesses and fintech</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Usually Series A and later</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>smallcase, M1xchange, Acko, FreshToHome, Cashify</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Rolling (investor, no cohort)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>https://smbhav.amazon.in/initiatives/smbhav-venture-fund</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Thesis matches 'digitise small businesses' but cheque stage is later; keep as a future investor lead.</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>https://smbhav.amazon.in/initiatives/smbhav-venture-fund</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n"/>
+      <c r="S40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Techstars Future of Food (powered by Ecolab)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Sector accelerator</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Techstars and Ecolab; Minneapolis-St. Paul</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>$220K ($20K for 5% via CEA plus $200K uncapped MFN SAFE), 3 months, Ecolab and food industry access</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Yes (5% plus SAFE)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to seed</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Milk Moovement ($20M Series A)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>2026 closed 10 Jun 2026 (cohort 8 Sep to 10 Dec 2026); next apps likely Mar to Jun 2027</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.techstars.com/accelerators/future-of-food</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Lists restaurant tech explicitly, but US-based, US-market focused and dilutive; only if TF wants a US angle.</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.techstars.com/accelerators/future-of-food</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Plug and Play Travel &amp; Hospitality / Food &amp; Beverage / Brand &amp; Retail</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Sector accelerator (corporate pilots)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Plug and Play; Silicon Valley (India office in Hyderabad)</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>3 months of workshops, dealflow sessions, intros to corporate partners for pilots</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>No (programs are equity-free; separate VC arm may invest)</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Seed to growth with a product corporates can pilot</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026: 140 startups across 13 programs, 55% non-US</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Fall 2026 batch announced 29 Sep 2026; twice-yearly batches, next TBA</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.plugandplaytechcenter.com/</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Corporate partners are mostly US hotel and food majors, not Indian independent restaurants; low fit today.</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>http://www.prnewswire.com/news-releases/plug-and-play-announces-silicon-valley-fall-batches-of-2026-302892764.html</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>FoodTech 500 (Forward Fooding)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Sector ranking / visibility program</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Forward Fooding; London, online</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Global ranking of food tech startups, exposure to investors and corporates, whitepaper Q1 2027</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>No, free to apply</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Incorporated, active website, under 15 years</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>500 AgriFoodTech startups ranked yearly</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>15 Nov 2026 (may close early)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://forwardfooding.typeform.com/to/dWJC4PbZ</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Free credibility badge for the deck; low effort once the company is incorporated, low direct value.</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/28/foodtech-500-competition-2026/</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>NRAI (National Restaurant Association of India)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Industry body (no accelerator)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>NRAI; New Delhi, city chapters</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>No startup program found; events like the Food Delivery Summit (20 Aug 2026, Ahmedabad, theme 'Automate to Dominate') offer restaurant access and vendor sponsorship slots</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Tech vendors appear as summit partners (e.g. Ownly in 2026)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Event based; next summit TBA</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>https://nrai.org/</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>A sales channel, not funding; worth a membership or chapter intro once TF expands beyond Bhubaneswar.</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>https://mediabrief.com/nrai-food-delivery-summit-returns-for-5th-edition/</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Freshworks for Startups</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Freshworks via Startup India</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>$4,000 credits for DPIIT startups ($10,000 for tax-exempt)</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT-recognised</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Rolling after DPIIT</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/reources/resource-partners/application-based-services/freshworks.html</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Only if TF needs a helpdesk; overlaps with Zoho credits.</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupindia.gov.in/content/sih/en/reources/resource-partners/application-based-services/freshworks.html</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>MeitY SAMRIDH via ABIF IIT Kharagpur (Cohort 2 accelerator)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Govt accelerator (matched investment)</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Agri Business Incubation Foundation, IIT Kharagpur, West Bengal</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 40L matched support plus possible extra grant up to Rs 5L; labs, mentoring</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Yes (SAMRIDH SAFE/CCPS)</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT Pvt Ltd, tech startup with initial traction, raising private money. Multi-sector incl FinTech, Supply Chain</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Agri and deeptech portfolio</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Program page says open, but the Cohort-II form (created 29 Apr 2026) is set to not accepting responses. 5 slots assigned</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://abif.iitkgp.ac.in/apply/samridh</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Second-closest SAMRIDH host (Kharagpur, about 4 hours from Bhubaneswar). Email office@abif.iitkgp.ac.in to ask about remaining slots.</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>https://abif.iitkgp.ac.in/programs/samridh</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>MeitY SAMRIDH (other Cohort 2 accelerators)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Govt accelerator (matched investment)</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>31 accelerators incl NSRCEL IIMB, IIMA Ventures, FITT IIT Delhi, India Accelerator, IIM Lucknow EIC, Indigram, AIC-SMUTBI Sikkim, Kalpataru CoE Vizag</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Avg Rs 30L, up to Rs 40L MSH investment matched 1:1 with accelerator/investor money; 5 to 10 startups per cohort</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Yes (SAFE to CCPS)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT, 51% Indian, MVP/early traction, investor commitment</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>SAMRIDH has 175 startups in cohort 1 across 22 accelerators</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Each accelerator runs its own window; most Cohort-2 calls ran 2025 to mid 2026 and show closed (e.g. IIM Udaipur). No Cohort 3 announced</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://msh.meity.gov.in/schemes/samridh</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Worth a fallback email to 3 or 4 hosts with open slots. IIM Calcutta (IIMCIP) was cohort 1 only and is not in cohort 2.</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>https://msh.meity.gov.in/assets/samridh2ndcohrot/SAMRIDH%202nd%20Cohort%20OM%20Final.pdf</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MeitY GENESIS Pilot Funding via FTBI NIT Rourkela</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Govt scheme (pilot funding) via incubator</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>FTBI, NIT Rourkela, Odisha</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 40L (equity-based) to run a paid pilot with a corporate or PSU</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Working MVP plus a valid purchase or work order from an eligible corporate/PSU</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>FTBI supports 115 startups</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Closed 24 Sep 2026; next call TBA. EIR Cohort 3 (Rs 10L, idea stage) closed 3 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ftbi-nitrkl.org/meity-genesis</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Only works if TF lands an enterprise order (for example a hotel chain, OTDC or a PSU canteen). Park until then.</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ftbi-nitrkl.org/meity-genesis</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>STPI LEAP Ahead (and NGIS / Chunauti)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Govt accelerator (seed)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Software Technology Parks of India, MeitY (STPI Bhubaneswar is a local centre)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Initial Rs 25L plus follow-on up to Rs 25L, mentoring, global connects</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Not stated in coverage; check terms</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Tier-II/III tech startups with revenue and investor interest</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Edition 1: 17 startups raised up to Rs 38 Cr</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Edition 2 (Chunauti 10) closed 15 Jan 2025. No edition 3 announced as of Sep 2026</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://leapahead1.stpi.in/</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Good money and Bhubaneswar is Tier-II, but no live call. Watch STPI announcements.</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>https://inc42.com/buzz/stpi-to-back-25-startups-under-leap-ahead-2-0/</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>AIC-SOA Foundation</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Atal Incubation Centre (AIM)</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Siksha O Anusandhan University, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Incubation, mentoring, infrastructure, industry links</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Rolling Google form</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdmgquL03Iq2nb3KUx2ElLiouEV60ju7Vc2wbz2eHJV_jb9lA/viewform</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Incubation only on current info; low value vs KIIT-TBI or AIC-Nalanda.</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aicsoa.in/</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>IIT Bhubaneswar Research and Entrepreneurship Park (REP) incubation / 100 Cube</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>University incubator</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>IIT Bhubaneswar REP, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Office space, mentors, investor facilitation; 100 Cube aims to back 100 Odisha startups to Rs 100 Cr by 2036; has invested in 39 companies</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Likely for 100 Cube investment; not published</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Portfolio incl application and business software startups</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Rolling Google form. TomorrowLAB accelerator (Tata Steel) is industrial only</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>https://rep.iitbbs.ac.in/incubation-program/</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>IIT brand helps with investors, but no published cash program for SaaS. Worth a conversation about 100 Cube.</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>https://rep.iitbbs.ac.in/incubation-program/</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>IIM Sambalpur I-Hub Acceleration Programme</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>University accelerator</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>IIM Sambalpur I-Hub Foundation, Sambalpur (also Delhi chapter)</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Mentors, funding access, strategic guidance, space, market access; 6 startups funded so far</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Growth-focused; preference for Fintech, Agritech, Textiles, Digital and Financial Inclusion, women-led</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>34+ startups supported</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>2025-26 edition closed 31 Jul 2025; 2026-27 edition TBA</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>https://ihub.iimsambalpur.ac.in/programme.php</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Odisha IIM program with fintech preference, but little money disclosed. Apply if a 2026-27 call opens.</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>https://ihub.iimsambalpur.ac.in/programme.php</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>FTBI NIT Rourkela incubation (MCL Seed Grant, NIDHI Prayas, TIDE 2.0)</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>University incubator (scheme gateway)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Foundation for Technology and Business Incubation, NIT Rourkela</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>MCL CSR seed grant; NIDHI Prayas up to Rs 10L; GENESIS centre</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Varies by scheme</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage, tech</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>115 startups supported</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>MCL Seed Grant 2026 closed 20 Aug 2026; NIDHI-EIR round 5 open</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ftbi-nitrkl.org/</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Mostly prototype-stage grants. Useful only as a second GENESIS host.</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ftbi-nitrkl.org/</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Switchtech Incubator Foundation (Silicon Institute of Technology)</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>University incubator</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Silicon Institute of Technology, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Incubation space (campus, DLF Cybercity, Infocity), mentors, help raising seed</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage tech</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>14 startups incubated</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>https://silicon.ac.in/business-incubator/</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha recognised incubator, but small and incubation only.</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>https://silicon.ac.in/news-post/startup-odisha-recognizes-silicon-institute-of-technology-bhubaneswar-as-an-incubator/</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>BharatNetra Innovation Accelerator</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>State govt accelerator (fintech)</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Govt of Odisha with Global Finance and Technology Network (GFTN), Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid program with monthly in-person sessions in Bhubaneswar, global fintech mentors; free</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Fintech, InsurTech, embedded finance. Accelerator needs over 18 months since incorporation plus revenue/funding; incubator track is for under 18 months</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25 fintechs in incubator cohort 1 (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Accelerator started 18 Jun 2026; incubator cohort 2 registration open, date not published</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>https://registration.gftn.co/</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Only fits if TF pitches the Razorpay Route payments layer as embedded finance. New Table Foundry entity would fit the incubator track, not the accelerator.</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>https://odisha.gftn.co/startupprogrammes</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>IIT Kharagpur STEP / TIETS / Entrepreneurship Seed Fund</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>University incubator</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>IIT Kharagpur (STEP since 1986, TIETS), West Bengal</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Seed grants, soft loans, milestone-based funds; access to PRISM, BIRAC schemes</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Mostly IIT KGP linked founders and tech ventures</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>100+ incubations</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Entrepreneurship Seed Fund rolling; Platinum Jubilee Seed Fund closed 10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>https://respark.iitkgp.ac.in/entrepreneurship-policy</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>Useful mainly if a founder has an IIT KGP link; otherwise ABIF SAMRIDH is the IIT KGP route.</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>https://respark.iitkgp.ac.in/entrepreneurship-policy</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Webel-BCC&amp;I Tech Incubation Centre</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>State-linked incubator</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Webel with Bengal Chamber of Commerce, Kolkata</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Incubation, ideathon, corporate accelerator tie-ups</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage tech</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Hornet Decentratech (raised Rs 4 Cr, 2025)</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Rolling; West Bengal new startup policy due after Aug 2026</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bengalchamber.com/techincubation/index.html</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Small; only relevant if TF opens Kolkata operations.</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bengalchamber.com/techincubation/index.html</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>TiE Kolkata programs</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Regional network / mentoring</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>TiE Kolkata chapter</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Mentoring, pitch readiness, angel exposure</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 startup cohort found (only student TYE program)</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>https://kolkata.tie.org/</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Networking only; lower priority than TiE Bhubaneswar.</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>https://events.tie.org/TiEYoungEntrepreneursProgram2026</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>IIMA Ventures (CIIE.CO) seed programs</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>University accelerator / fund</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>IIMA Ventures, IIM Ahmedabad</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed cheques; runs a SAMRIDH Cohort 2 slot (8 startups) and Kotak BizLabs S3</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Yes for investments</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to seed</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>300+ startups backed, incl Ola</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>SAMRIDH window not open; Kotak BizLabs closes 6 to 9 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>https://iimaventures.com/programs/kotak-bizlabs-3-0/</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Worth a direct pitch for the pre-seed round; accelerator route mostly via Kotak.</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>Angel networks</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>https://iimaventures.com/programs/kotak-bizlabs-3-0/</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>NSRCEL IIM Bangalore (Launchpad, Velocity, SAMRIDH)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>University accelerator</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>NSRCEL, IIM Bangalore</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Launchpad: 5-month pre-incubation, Rs 5L grant for top startups. Velocity = Kotak BizLabs grant up to Rs 30L. Also a SAMRIDH Cohort 2 host</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>No for Launchpad and Velocity</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Launchpad: idea to MVP. Velocity: revenue-stage</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>3,657+ ventures incubated</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Launchpad 30 closed 5 Apr 2026; Velocity uses the Kotak deadline</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>https://nsrcel.org/velocity/</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Use the Kotak form; Launchpad is too early for TF.</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>https://nsrcel.org/velocity/</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>FITT IIT Delhi (SAMRIDH host)</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>University accelerator</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Foundation for Innovation and Technology Transfer, IIT Delhi</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>SAMRIDH Cohort 1 and 2 accelerator (8 slots in Cohort 2); Kotak BizLabs S3 partner</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Yes for SAMRIDH (SAFE to CCPS)</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Software product startups with PoC and investor interest</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>300+ startups</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>No open SAMRIDH window found</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>https://fitt-iitd.in/web/samridh</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Far from Odisha; only a fallback SAMRIDH host.</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>https://fitt-iitd.in/web/samridh</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>SINE IIT Bombay NIDHI-SSP / SIDBI seed</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>University incubator (scheme gateway)</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>SINE, IIT Bombay, Mumbai</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>NIDHI-SSP equity/CCPS up to Rs 1 Cr; SIDBI-funded seed Rs 25L to 1 Cr for incubatees</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT Pvt Ltd; external startups must incubate (physical or virtual) with SINE</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Large deeptech portfolio</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Calls in June 2026 closed; next TBA</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sineiitb.org/</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Deeptech bias. KIIT-TBI is the nearer NIDHI-SSS host.</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupgrantsindia.com/providers/sine-iit-bombay</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>C: long shot / conditional</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Zone Startups India (BSE)</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Exchange-backed accelerator</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Zone Startups India, Mumbai (BSE Institute and Toronto Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>4 to 6 month programs, corporate access, mentors; SAMRIDH Cohort 1 host (AcceleratHER for women founders)</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Only if seed funded: 5 to 7%</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage tech</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>550+ startups supported</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 window found</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>https://india.zonestartups.com/</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>Not in SAMRIDH Cohort 2; low priority.</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>https://india.zonestartups.com/samridh</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Upekkha AI Accelerator</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Services-for-equity accelerator</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Upekkha / Bengaluru</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>No cash now per apply page: 2 to 4% equity plus milestone success fees; US immersion, mentors, credits</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 2 to 4% (no cash)</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Early revenue, about $100K ARR, AI-first B2B</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Thrive (restaurant direct ordering, a TF comparable)</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Latest intake closed 6 Sep 2026; next TBA</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.upekkha.io/apply</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Too early and no cash: revisit near $100K ARR; alumni Thrive shows the playbook works for restaurant SaaS.</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>Micro-VCs &amp; angel funds</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.upekkha.io/apply</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Google for Startups Accelerator: India (AI-first)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Google; Bengaluru, hybrid</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>3 months, Google mentors (DeepMind, Cloud, Android), early access to Gemini and other models, cloud credits and TPUs, demo day</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Seed to Series A, India HQ, AI-first with traction</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>2026: 20 startups incl. SpotDraft, TrueFoundry, Dodo Payments, GobbleCube, Swish Club (from about 2,500 applications)</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Next cohort TBA; last cycle closed 19 Apr 2026 (cohort Jun to Sep 2026). Expect apps around Mar to Apr 2027</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>https://startup.google.com/programs/accelerator/india/</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Agentic AI for restaurants fits the 2026 theme, but TF needs the seed round and more restaurants live to be competitive; target the 2027 cycle.</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>https://startup.google.com/programs/accelerator/india/</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>AWS Generative AI Accelerator</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator (credits)</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>AWS; Seattle kickoff, virtual, ends at re:Invent</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Up to $1M AWS credits, mentors, 8 weeks, demo at re:Invent</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Up to Series A, under 5 years, product built, early revenue</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Indian picks incl. Hyperbots, Smallest AI, Stimuler (2025)</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>2026 window was 10 Jun to 10 Jul 2026 (closed); next expected mid-2027</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/startups/programs/generative-ai</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Global, about 40 picks and under 2% acceptance; TF is an AI application, not a model company, so a long shot.</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>https://startupintros.com/resources/aws-generative-ai-accelerator-2026</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Mastercard Start Path Small Business</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Mastercard; global, virtual</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>About 4 to 6 month program, mentor, access to Mastercard teams, banks and merchants, demo days</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Seed or later raised, product live, generating revenue</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>5 startups joined Apr 2026; 500+ Start Path alumni overall</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Rolling intake into periodic cohorts</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mastercard.com/global/en/innovation/partner-with-us/start-path/small-business.html</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>SMB merchant tools fit, but TF is pre-seed and card payments matter less than UPI for Indian restaurants; revisit after the seed round.</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mastercard.com/global/en/business/fintech/fintech-programs/startpath/for-startups/small-business.html</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="n"/>
+      <c r="S67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>T-Hub T-Angel and Lab32</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Govt-backed accelerator (Telangana)</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>T-Hub, Hyderabad</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>T-Angel: 100 to 120 day investment-readiness sprint and VC/angel demo day. Lab32: 100-day market-readiness program</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>No equity stated</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>T-Angel wants PMF and Rs 3 to 5L MRR, raising $250K to $750K. Lab32: early revenue</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>286 Lab32 startups over 11 cohorts</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>T-Angel closed; Lab32 rolling expression of interest</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.t-hub.co/programs</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>T-Angel matches TF's raise size, but 3 restaurants likely sit below the Rs 3 to 5L MRR bar. Revisit at 15 to 20 restaurants.</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.t-hub.co/programs</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R68" s="5" t="n"/>
+      <c r="S68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>HF0 Residency</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Live-in residency</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>HF0 / San Francisco</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Reported up to $1M uncapped SAFE for 5%; housing and meals (terms not published by HF0)</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Yes, reported 5%</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Repeat or exceptional technical founders</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Next cohort TBA</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hf0.com</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Wrong fit: tiny frontier-tech cohorts in SF.</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>https://hub.causo.ai/guides/how-to-apply-to-hf0-residency-2026</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R69" s="5" t="n"/>
+      <c r="S69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Techstars</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Techstars / global (no India program listed)</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>$220K: $20K for 5% common plus $200K uncapped MFN SAFE (APAC programs: $100K MFN SAFE variant)</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 5% plus MFN</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to seed</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Techstars Bangalore alumni (2019 to 2021 cohorts)</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>No India cohort; Bangalore no longer on Techstars accelerator list; Fall 2026 London/NYC deadlines passed (14 Sep 2026); Anywhere is North America only</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.techstars.com/accelerators</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Skip for now: no program TF can realistically join in 2026.</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr"/>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.techstars.com/newsroom/investment-terms ; https://www.techstars.com/accelerators</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="n"/>
+      <c r="S70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Alchemist Accelerator</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator (B2B enterprise)</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Alchemist / San Francisco, remote</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Average $30K net of tuition for about 5% common</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Yes, about 5%</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Any stage; must monetize from enterprises</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise AI SaaS globally</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Rolling deadlines; decisions within 3 weeks</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alchemistaccelerator.com/apply</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Wrong fit: wants enterprise revenue, TF sells to small restaurants.</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alchemistaccelerator.com/flagship-program</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R71" s="5" t="n"/>
+      <c r="S71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>AI Grant</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Cash accelerator (AI)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>AI Grant (Nat Friedman, Daniel Gross) / SF</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>$250K uncapped SAFE plus $350K Azure and $250K other credits</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Yes, uncapped SAFE</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed AI startups; must be Delaware C-corp</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Batch 4 closed; no batch open</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>https://aigrant.com</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Skip: closed and needs Delaware.</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr"/>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>https://aigrant.com</t>
+        </is>
+      </c>
+      <c r="P72" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R72" s="5" t="n"/>
+      <c r="S72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Neo Residency</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Cash residency</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Neo / US</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>$750K uncapped SAFE plus participation rights up to 5%</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Yes, via uncapped SAFE</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Early technical teams (US focus)</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Replaced old accelerator in Feb 2026; timing TBA</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>https://neo.com</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>Skip: US-centric technical residency.</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
+          <t>https://hub.causo.ai/guides/how-to-apply-to-neo-accelerator-2026</t>
+        </is>
+      </c>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R73" s="5" t="n"/>
+      <c r="S73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Sequoia Arc</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed immersion</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Sequoia Capital / US, Europe</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>$500K to $1M, company-specific terms</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed to seed</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Open call only for Americas and Europe HQ</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sequoiacap.com/arc/</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Skip: India-HQ companies are not eligible; Peak XV Surge is the India equivalent.</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr"/>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>https://hub.causo.ai/guides/how-to-apply-to-sequoia-arc-2026</t>
+        </is>
+      </c>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R74" s="5" t="n"/>
+      <c r="S74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Lightspeed India Ascends</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Pre-seed program</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Lightspeed India</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>$200K to $3M for 3 to 4 winners plus about $500K credits</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Founders under 25, R&amp;D-first deeptech</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Sapien Labs, Eyecandy Robotics</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>2026 cohort announced Feb 2026; next TBA</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>https://lsvp.com</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Wrong fit: deeptech and under-25 only.</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>https://yourstory.com/2026/02/lightspeed-selects-4-deeptech-startups-for-its-india-ascends-2026-cohort</t>
+        </is>
+      </c>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R75" s="5" t="n"/>
+      <c r="S75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Orios Misfits</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Accelerator fund</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Orios Venture Partners / Mumbai</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>$500K to $1.5M for 10 to 20%</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 10 to 20%</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Early stage</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Applications closed; no new cohort found</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>https://oriosvp.com</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Skip: no open cohort and heavy equity.</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr"/>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ellenox.com/post/india-startup-accelerators</t>
+        </is>
+      </c>
+      <c r="P76" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q76" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R76" s="5" t="n"/>
+      <c r="S76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Z47 (Matrix India) / Elevation Capital programs</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>VC (no open pre-seed program found)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Z47, Elevation / Bengaluru, Gurugram</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>No dedicated pre-seed cohort found in 2025 to 2026</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Seed to Series B</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Razorpay (Z47), others</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.z47.com</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Skip as accelerators; approach later as Series A investors.</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t>https://superscout.co/investor/z47-fka-matrix-partners-india</t>
+        </is>
+      </c>
+      <c r="P77" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Startup India Seed Fund via KIIT-TBI Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Cash / equity</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Govt seed fund via incubator</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT via KIIT-TBI / Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Was up to Rs 20L grant plus up to Rs 50L convertible debentures</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>No (debentures may convert)</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT-recognised early startups</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>KIIT-TBI Eastern India portfolio</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>SISFS closed: last date 31 May 2026; no successor announced as of Sep 2026</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>https://seedfund.startupindia.gov.in</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Skip for now, but watch for a new SISFS cycle since KIIT-TBI is in TF's city.</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
+          <t>https://srfcapital.studio/resources/articles/startup-india-seed-fund-what-happened</t>
+        </is>
+      </c>
+      <c r="P78" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q78" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Meta Startup School (India)</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Corporate growth program</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Meta India with agency partners</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>3 months of free agency consultation, Meta ads and AI tools training, VC access (Fireside, DSG Consumer Partners, V3), demo day</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage consumer brands starting to scale revenue on Meta, not already with an agency</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>First cohort of 200 started 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Cohort 1 started 1 Sep 2026; next cohort TBA</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Meta Startup School programme page (link not published in the announcement)</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>Built for D2C consumer brands, not B2B SaaS; only useful as a referral for TF's restaurant clients if Meta opens it to them.</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t>https://about.fb.com/news/2026/08/launching-meta-startup-school-to-accelerate-growth-for-early-stage-startups/</t>
+        </is>
+      </c>
+      <c r="P79" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Meta Llama Startup Program</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Credits program</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Was up to $6K per month cloud reimbursement for 6 months plus Meta support</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>US-incorporated, under $10M raised</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Inaugural cohort 2025</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>US only; Meta's developer focus has shifted to the paid Meta Model API (Muse Spark, Jul 2026, $20 starter credit)</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.llama.com/llama-ai-innovation/</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>Not open to an Indian company; nothing to apply for.</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr"/>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
+          <t>https://ai.meta.com/blog/llama-startup-program/</t>
+        </is>
+      </c>
+      <c r="P80" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q80" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R80" s="5" t="n"/>
+      <c r="S80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Meta-MeitY XR Startup Program</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Corporate + government accelerator</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Meta and MeitY Startup Hub, via FITT IIT Delhi</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Rs 20 lakh grant, 6 months mentoring</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage XR startups</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>10 XR startups per cohort</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 call found</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>https://fitt-iitd.in/web/meta</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>XR only; no fit for TF.</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t>https://fitt-iitd.in/web/meta</t>
+        </is>
+      </c>
+      <c r="P81" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q81" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R81" s="5" t="n"/>
+      <c r="S81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Google Play Accelerator India (successor to Appscale Academy)</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Google Play; India</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>3 months, app quality, AI integration, growth and monetisation help</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>App-first startups</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>2026 cohort: Swipe, UrbanPro, Zet, MrMed, Kisanwala and 15 others</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>2026 apps closed 24 May 2026; cohort runs Jul to Nov 2026</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>https://startup.google.com/programs/accelerator/apps/india/</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>Built for Play Store apps; TF lives on WhatsApp and web, so weak fit.</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>https://india.entrepreneur.com/business-news/google-unveils-2026-cohort-of-google-play-accelerator-india</t>
+        </is>
+      </c>
+      <c r="P82" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q82" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R82" s="5" t="n"/>
+      <c r="S82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Visa Everywhere Initiative / Visa Accelerator (APAC)</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Pitch competition / corporate accelerator</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Prize money or pilot work with Visa and its partner banks</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>APAC accelerator asked for Series A and above</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Past India edition focused on digital payments beyond metros</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>No live 2026 India or APAC call found</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.visa.co.in/about-visa/newsroom/press-releases/visa-invites-india-top-startups-to-shape-the-future-of-payments.html</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>No current India call and stage bar is too high.</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.visa.co.in/about-visa/newsroom/press-releases/visa-invites-india-top-startups-to-shape-the-future-of-payments.html</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q83" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R83" s="5" t="n"/>
+      <c r="S83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Paytm for Startups / PhonePe / Pine Labs</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Payment perks (no accelerator)</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Paytm, PhonePe, Pine Labs</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Paytm: discounted payment products for registered startups, plus a DPIIT tie-up aimed at payment hardware makers. PhonePe and Pine Labs: no startup program found</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Startup India or incubator-registered</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Rolling (Paytm perks)</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>https://business.paytm.com/paytm-startups</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>TF is on Razorpay; nothing here beyond cheaper payments.</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2106337</t>
+        </is>
+      </c>
+      <c r="P84" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q84" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R84" s="5" t="n"/>
+      <c r="S84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Bank fintech accelerators (Axis Thought Factory, YES FINTECH, ICICI-IIML Finovate)</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Corporate fintech accelerators</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Axis Bank, YES Bank, ICICI Bank with IIM Lucknow EIC</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Bank pilots, mentors, investor connects</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Mostly no</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Fintech startups selling to banks</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Axis: Perpule, S2Pay (early cohorts)</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 Axis cohort found; YES and ICICI run fintech-for-banks calls</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yesfintech.com/</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>They want B2B banking tech; TF sells to restaurants.</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iimleic.com/finovate-acceleration-program</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q85" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R85" s="5" t="n"/>
+      <c r="S85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Cisco LaunchPad</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerator</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Cisco; Bengaluru</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>6 months, co-working, mentors, Cisco tech platforms</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Mid to late stage B2B deep tech</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>6-8 startups per cohort in networking, security, IoT</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Periodic via Startup India; no relevant 2026 call</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>https://startups.cisco.com/</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>Networking and security focus; no fit.</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr"/>
+      <c r="O86" s="5" t="inlineStr">
+        <is>
+          <t>https://startups.cisco.com/c/faqs.html</t>
+        </is>
+      </c>
+      <c r="P86" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q86" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R86" s="5" t="n"/>
+      <c r="S86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Swiggy / Zomato programs</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>No startup accelerator</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Swiggy, Zomato (Eternal)</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>No startup program found; Swiggy Launchpad is a zero-commission first month for new restaurants, not for tech startups</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>Aggregators are TF's competition for restaurant margin; no program to join.</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t>https://inc42.com/buzz/swiggy-takes-on-zomato-with-0-commission-strategy/</t>
+        </is>
+      </c>
+      <c r="P87" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q87" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R87" s="5" t="n"/>
+      <c r="S87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Food and hotel corporates (Jubilant FoodWorks, IHCL, ITC, Tata, HUL, Nestle, Coca-Cola, PepsiCo Greenhouse)</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Corporate accelerators (none open to TF)</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>No startup program found for Jubilant, IHCL, ITC, HUL, Nestle or Coca-Cola in 2025-2026. PepsiCo Greenhouse APAC 2026 is alumni-only and sustainability focused</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>PepsiCo APAC 2026: Adiona, X-Centric</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>None open</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>Nothing to apply for; chains are a sales target at most, not an accelerator path.</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr"/>
+      <c r="O88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pepsico.com/en/newsroom/press-releases/2026/pepsico-unveils-2026-greenhouse-program-impact-edition-in-asia-expanding-sustainability-solutions</t>
+        </is>
+      </c>
+      <c r="P88" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q88" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R88" s="5" t="n"/>
+      <c r="S88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Walmart Vriddhi</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>MSME supplier development program</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Walmart and Flipkart</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Training and marketplace access for MSME sellers and exporters</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>MSME product sellers</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>115,000+ MSMEs trained</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Rolling events (e.g. Kolkata MSME Connect, Sep 2026)</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.walmartvriddhi.org/</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>For product sellers, not software startups.</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.walmartvriddhi.org/en/newsroom/walmart-vriddhi-msme-connect-kolkata-2026-brings-market-access-and-export-readiness-into-focus-for-west-bengal-entrepreneurs</t>
+        </is>
+      </c>
+      <c r="P89" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q89" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Global food accelerators (Brinc, Big Idea Ventures, Toast Lab)</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Corporate / sector</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Sector accelerators</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Brinc (HK), Big Idea Ventures (NYC/Paris/Singapore), Toast (Boston)</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Brinc and BIV: small equity cheques for alt-protein and food products, often with fees. Toast Lab: funds one Boston restaurant opening</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Yes for Brinc and BIV</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Food product startups</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Alt-protein brands</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Rolling (Brinc, BIV); Toast Lab closed 14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>Food science and restaurant operators, not restaurant software.</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr"/>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.failory.com/startups/foodtech-accelerators-incubators</t>
+        </is>
+      </c>
+      <c r="P90" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q90" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R90" s="5" t="n"/>
+      <c r="S90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>STPI Centres of Entrepreneurship in Odisha and East (EP Bhubaneswar, VARCOE, EmTek Rourkela, OCTANE North East)</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Govt CoE incubator</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>STPI, Bhubaneswar / Rourkela / Guwahati</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Domain labs and incubation in ESDM, AR/VR, electronics; OCTANE is North East only</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Hardware and domain startups</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>EP Bhubaneswar runs Open Challenge Program rounds (OCP-8)</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>https://stpi.in/en/stpi-coe</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>Wrong domain for a restaurant SaaS. No STPI CoE in Bengal, Bihar or Jharkhand.</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr">
+        <is>
+          <t>https://stpi.in/en/stpi-coe</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q91" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R91" s="5" t="n"/>
+      <c r="S91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha Yatra 2.0</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>State outreach program</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Startup Odisha</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Van campaigns and bootcamps in 30+ districts; cash prizes for top 10 ideas, incubation for selected ideas</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Students and idea-stage</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>Periodic; no current round found</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>https://startupodisha.gov.in/latest_events/startup-odisha-yatra-2-0/</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>Built for student and grassroots ideas, not a revenue-stage company.</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr"/>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
+          <t>https://startupodisha.gov.in/latest_events/startup-odisha-yatra-2-0/</t>
+        </is>
+      </c>
+      <c r="P92" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q92" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R92" s="5" t="n"/>
+      <c r="S92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Startup Jharkhand SAKSHAM 4.0</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Regional accelerator</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Startup Jharkhand (Section 8), Ranchi</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>6 to 8 week mentoring: fundraising readiness, market access incl govt procurement</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage startups in Jharkhand</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>Site says 2 Oct 2026 (other listing said 15 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>https://startupjharkhand.org/</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>Built for Jharkhand-based startups; TF is not.</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr">
+        <is>
+          <t>https://startupjharkhand.org/</t>
+        </is>
+      </c>
+      <c r="P93" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q93" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Bihar Startup Policy / IIT Patna Incubation Centre</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>State scheme + university incubator</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Govt of Bihar; IC IIT Patna (also a GENESIS host)</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Bihar seed fund: interest-free loan up to Rs 10L (Rs 25L announced Jan 2026); IIT Patna runs GENESIS EIR/Pilot/Matching tracks</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>No for Bihar loan; GENESIS takes equity</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Bihar-certified startups registered with a Bihar incubator</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>https://iciitp.com/index.php/genesis-2/</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>Needs Bihar registration; TF will be an Odisha company. Use KIIT-TBI for GENESIS instead.</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr">
+        <is>
+          <t>https://iciitp.com/index.php/genesis-2/</t>
+        </is>
+      </c>
+      <c r="P94" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q94" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R94" s="5" t="n"/>
+      <c r="S94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>36Inc (AIC@36Inc), Raipur</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>State + Atal incubator</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Govt of Chhattisgarh and AIM, Raipur</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Incubation, mentoring, market linkages, funding access</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Chhattisgarh startups; agri, mining, drone, urban</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>48 startups</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 cohort found</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>https://36inc.in/</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>Chhattisgarh focus, no fit for an Odisha company.</t>
+        </is>
+      </c>
+      <c r="N95" s="5" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
+          <t>https://36inc.in/</t>
+        </is>
+      </c>
+      <c r="P95" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q95" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R95" s="5" t="n"/>
+      <c r="S95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>IIT Madras Incubation Cell (TECHPIONEER)</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>University incubator</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>IIT Madras Incubation Cell, Chennai</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Grant up to Rs 50L, no equity, for growth-stage deeptech</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>No for grant</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Deeptech, SDG-aligned, DPIIT</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>500+ startups incubated</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>Closed 31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupgrantsindia.com/providers/iit-madras-incubation-cell</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>Deeptech only; a WhatsApp ordering SaaS will not qualify.</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupgrantsindia.com/techpioneer-grant-program-at-iit-madras-incubation-cell-317</t>
+        </is>
+      </c>
+      <c r="P96" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q96" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R96" s="5" t="n"/>
+      <c r="S96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Kerala Startup Mission (ELEVATE, SCALE)</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>State accelerator</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>KSUM, Kerala</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 15L (ELEVATE) and Rs 50L (SCALE)</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Mostly no</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Kerala-registered Pvt Ltd with KSUM ID</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>961 startups</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>https://startupmission.kerala.gov.in/</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>Needs a Kerala company.</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.startupgrantsindia.com/providers/kerala-startup-mission</t>
+        </is>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="Q97" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R97" s="5" t="n"/>
+      <c r="S97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Startup India Seed Fund Scheme (SISFS)</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Govt seed scheme via incubators</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT via 300 incubators (KIIT-TBI, AIC-Nalanda, IIT Patna etc)</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Up to Rs 20L grant and Rs 50L debt/convertible</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Convertible for the Rs 50L part</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>DPIIT, under 2 years</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Closed to new applications 31 May 2026; incubators had to finish selection by 30 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>https://seedfund.startupindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>Scheme has ended. Do not plan around it unless a successor is announced.</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O98" s="5" t="inlineStr">
+        <is>
+          <t>https://seedfund.startupindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="P98" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q98" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R98" s="5" t="n"/>
+      <c r="S98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>Skip: closed or wrong fit</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>MeitY TIDE 2.0 (EIR and Grant)</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Govt / regional</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Govt grant via incubator</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>MeitY via KIIT-TBI, IIMCIP, FTBI</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>EIR Rs 4L; Grant Rs 7L for 12 months</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Idea to PoC; first-generation founders</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>IIMCIP round closed 25 Aug 2025; KIIT shows call closed</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iimcip.org/meity-tide2/</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>Too small and too early for a revenue-stage company.</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>Grants &amp; non-VC money</t>
+        </is>
+      </c>
+      <c r="O99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iimcip.org/meity-tide2/</t>
+        </is>
+      </c>
+      <c r="P99" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q99" s="5" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="R99" s="5" t="n"/>
+      <c r="S99" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S99"/>
+  <dataValidations count="1">
+    <dataValidation sqref="Q2:Q99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not contacted,Warm intro asked,Contacted,Replied,Meeting booked,Passed,Committed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/TF_PreSeed_Investor_List_30Sep2026.xlsx
+++ b/TF_PreSeed_Investor_List_30Sep2026.xlsx
@@ -709,14 +709,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SIDBI Innovation Challenge closes 16 Oct 2026. It fits if TF is pitched as AI-led market access for small restaurants (MSMEs). With Kotak BizLabs (6 Oct) and YC (2 Nov), it is one of three hard deadlines right now.</t>
+          <t>SIDBI Innovation Challenge closes 16 Oct 2026. It fits if TF is pitched as AI-led market access for small restaurants (MSMEs). With YC (2 Nov), it is one of two hard deadlines right now.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Kotak BizLabs Season 3 (grant up to Rs 30L, no equity) closes 6 Oct 2026 and needs DPIIT recognition by then. Only realistic if DPIIT lands this week, or if MSM Global already has it. Pick IIMCIP Kolkata as the partner and frame TF as fintech or inclusive tech.</t>
+          <t>Kotak BizLabs Season 3 (grant up to Rs 30L, no equity) closes 6 Oct 2026. TF will miss it because DPIIT recognition won't be ready. Watch for Season 4; it is a strong fit once DPIIT is in place.</t>
         </is>
       </c>
     </row>
@@ -14005,9 +14005,9 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>A: apply first</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Later: next round</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -14082,7 +14082,11 @@
         </is>
       </c>
       <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>Missed Season 3 (no DPIIT by 6 Oct). Target Season 4 once Table Foundry Pvt Ltd has DPIIT recognition.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
